--- a/data/trans_orig/IP16A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>35949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>21885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>40369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>46652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>34484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39273</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>59286</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64573</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113010</t>
+          <t>112934</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121618</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127277</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137834</t>
+          <t>137597</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>244363</t>
+          <t>244198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257097</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>27414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43410</t>
+          <t>42593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>18922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24720</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40969</t>
+          <t>41145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48677</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>135791</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143741</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>145670</t>
+          <t>146094</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>285972</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>297460</t>
+          <t>297912</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24267</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38584</t>
+          <t>39043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44578</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121790</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>111647</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>120071</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>246001</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33520</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42836</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62204</t>
+          <t>61983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71363</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>170335</t>
+          <t>169891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>170272</t>
+          <t>170673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>179214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>344235</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
